--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH78"/>
+  <dimension ref="A1:BH80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
         <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -781,13 +781,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>1.99</v>
@@ -799,19 +799,19 @@
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
@@ -832,7 +832,7 @@
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>14</v>
@@ -862,7 +862,7 @@
         <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -874,7 +874,7 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -898,7 +898,7 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>22</v>
@@ -907,20 +907,20 @@
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -969,152 +969,152 @@
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.01</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I4" t="n">
-        <v>310</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="P4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.9</v>
       </c>
-      <c r="K4" t="n">
-        <v>950</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
         <v>1.01</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1357,152 +1357,152 @@
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>420</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>420</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.01</v>
       </c>
-      <c r="K6" t="n">
-        <v>950</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
         <v>3.45</v>
@@ -1951,34 +1951,34 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
         <v>32</v>
@@ -1999,7 +1999,7 @@
         <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
@@ -2038,7 +2038,7 @@
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
@@ -2074,17 +2074,17 @@
         <v>21</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
         <v>4.3</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>3.45</v>
       </c>
       <c r="G11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
         <v>2.04</v>
@@ -2515,10 +2515,10 @@
         <v>2.22</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
         <v>1.56</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
         <v>1.56</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J19" t="n">
         <v>4.6</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G21" t="n">
         <v>2.76</v>
@@ -4452,13 +4452,13 @@
         <v>2.42</v>
       </c>
       <c r="I21" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J21" t="n">
         <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
         <v>1.96</v>
       </c>
       <c r="H23" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>220</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>5.4</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G25" t="n">
-        <v>240</v>
+        <v>1.79</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>240</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="G26" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J26" t="n">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5828,10 +5828,10 @@
         <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
         <v>2.2</v>
@@ -5873,7 +5873,7 @@
         <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE28" t="n">
         <v>44</v>
@@ -5894,10 +5894,10 @@
         <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
         <v>140</v>
@@ -5906,10 +5906,10 @@
         <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
@@ -5930,10 +5930,10 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
@@ -5945,7 +5945,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC28" t="n">
         <v>25</v>
@@ -5960,11 +5960,11 @@
         <v>21</v>
       </c>
       <c r="BG28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H30" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>310</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6222,7 +6222,7 @@
         <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G32" t="n">
         <v>2.74</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G35" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I35" t="n">
         <v>2.9</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.92</v>
       </c>
       <c r="J35" t="n">
         <v>3.3</v>
@@ -7213,55 +7213,55 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="n">
         <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD35" t="n">
         <v>13.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG35" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ35" t="n">
         <v>44</v>
       </c>
       <c r="AK35" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL35" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM35" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO35" t="n">
         <v>28</v>
@@ -7276,7 +7276,7 @@
         <v>14.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT35" t="n">
         <v>9.4</v>
@@ -7288,7 +7288,7 @@
         <v>9.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX35" t="n">
         <v>16</v>
@@ -7300,19 +7300,19 @@
         <v>14</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF35" t="n">
         <v>18.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H36" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="I36" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="J36" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G37" t="n">
         <v>2.5</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G38" t="n">
         <v>2.64</v>
       </c>
       <c r="H38" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I38" t="n">
         <v>2.78</v>
@@ -7765,28 +7765,28 @@
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R38" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="T38" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U38" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7795,19 +7795,19 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="n">
         <v>42</v>
       </c>
       <c r="AB38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC38" t="n">
         <v>8.6</v>
@@ -7816,10 +7816,10 @@
         <v>12.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF38" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG38" t="n">
         <v>12.5</v>
@@ -7828,7 +7828,7 @@
         <v>15.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ38" t="n">
         <v>36</v>
@@ -7843,19 +7843,19 @@
         <v>65</v>
       </c>
       <c r="AN38" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AO38" t="n">
         <v>20</v>
       </c>
       <c r="AP38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR38" t="n">
         <v>18</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>18.5</v>
       </c>
       <c r="AS38" t="n">
         <v>36</v>
@@ -7882,36 +7882,36 @@
         <v>14</v>
       </c>
       <c r="BA38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB38" t="n">
         <v>32</v>
       </c>
       <c r="BC38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE38" t="n">
         <v>55</v>
       </c>
       <c r="BF38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG38" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7926,31 +7926,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A.E.L.</t>
+          <t>Nk Posusje</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="K39" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7965,10 +7965,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -8098,14 +8098,14 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8120,61 +8120,61 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Digenis Ypsona</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>A.E.L.</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H40" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="I40" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="K40" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8183,116 +8183,116 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="G41" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -8508,61 +8508,61 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="G42" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="H42" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="I42" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
         <v>4</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.68</v>
-      </c>
       <c r="T42" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="U42" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8571,123 +8571,123 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS42" t="n">
         <v>21</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AT42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX42" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z42" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI42" t="n">
+      <c r="AY42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD42" t="n">
         <v>44</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA42" t="n">
+      <c r="BE42" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF42" t="n">
         <v>36</v>
       </c>
-      <c r="BB42" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG42" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,30 +8697,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="H43" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J43" t="n">
         <v>4</v>
@@ -8732,31 +8732,31 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="O43" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="T43" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="U43" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8765,123 +8765,123 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF43" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AG43" t="n">
         <v>10.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ43" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK43" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL43" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA43" t="n">
         <v>38</v>
       </c>
-      <c r="AM43" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>30</v>
-      </c>
       <c r="BB43" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC43" t="n">
         <v>17</v>
       </c>
       <c r="BD43" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BE43" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF43" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8896,61 +8896,61 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P44" t="n">
         <v>2.08</v>
       </c>
-      <c r="G44" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.79</v>
-      </c>
       <c r="Q44" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8959,123 +8959,123 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,42 +9085,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="G45" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="H45" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="I45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K45" t="n">
         <v>3.75</v>
       </c>
-      <c r="J45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -9129,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9141,10 +9141,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -9153,123 +9153,123 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,67 +9279,67 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12:50:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="G46" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="H46" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U46" t="n">
         <v>2.28</v>
       </c>
-      <c r="I46" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
@@ -9347,123 +9347,123 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,36 +9473,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:50:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Enosis Neon Paralimni</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.16</v>
+        <v>2.8</v>
       </c>
       <c r="G47" t="n">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="H47" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="I47" t="n">
-        <v>80</v>
+        <v>2.62</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,14 +9650,14 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9672,31 +9672,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="G48" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="H48" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="I48" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,14 +9844,14 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9866,61 +9866,61 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.32</v>
+        <v>1.64</v>
       </c>
       <c r="G49" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="H49" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="I49" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K49" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.24</v>
+        <v>1.6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9929,123 +9929,123 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10060,61 +10060,61 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="G50" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="H50" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="J50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S50" t="n">
         <v>4.2</v>
       </c>
-      <c r="K50" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -10123,123 +10123,123 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10254,31 +10254,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="H51" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K51" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,14 +10426,14 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10448,31 +10448,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Enosis Neon Paralimni</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="G52" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I52" t="n">
-        <v>8.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="J52" t="n">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K52" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -10487,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -10620,14 +10620,14 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10637,36 +10637,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="G53" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="H53" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K53" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10681,10 +10681,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -10814,14 +10814,14 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10831,36 +10831,36 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="G54" t="n">
-        <v>1.72</v>
+        <v>3.75</v>
       </c>
       <c r="H54" t="n">
-        <v>5.1</v>
+        <v>2.18</v>
       </c>
       <c r="I54" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -10875,10 +10875,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -11008,14 +11008,14 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11030,61 +11030,61 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="G55" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="H55" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="R55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -11093,123 +11093,123 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11224,61 +11224,61 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="G56" t="n">
-        <v>2.92</v>
+        <v>1.49</v>
       </c>
       <c r="H56" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="J56" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="K56" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N56" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="P56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q56" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q56" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R56" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="T56" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="U56" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -11287,123 +11287,123 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y56" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC56" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z56" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA56" t="n">
+      <c r="AD56" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL56" t="n">
         <v>42</v>
       </c>
-      <c r="AB56" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC56" t="n">
+      <c r="AM56" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT56" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD56" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI56" t="n">
+      <c r="AU56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG56" t="n">
         <v>46</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>25</v>
-      </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11413,66 +11413,66 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="G57" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="H57" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="I57" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="J57" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K57" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P57" t="n">
-        <v>2.36</v>
+        <v>1.86</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -11481,116 +11481,116 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -11612,32 +11612,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.84</v>
+        <v>4.8</v>
       </c>
       <c r="G58" t="n">
-        <v>1.93</v>
+        <v>5.6</v>
       </c>
       <c r="H58" t="n">
-        <v>4.4</v>
+        <v>1.67</v>
       </c>
       <c r="I58" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K58" t="n">
         <v>4.8</v>
       </c>
-      <c r="J58" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
@@ -11651,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -11806,31 +11806,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="G59" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="I59" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="K59" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -11978,14 +11978,14 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11995,36 +11995,36 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Gyori</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Diosgyori</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="G60" t="n">
-        <v>1000</v>
+        <v>1.72</v>
       </c>
       <c r="H60" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I60" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="K60" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,14 +12172,14 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12189,36 +12189,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Gyori</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Diosgyori</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="G61" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="H61" t="n">
-        <v>3.15</v>
+        <v>13</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="J61" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12233,10 +12233,10 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -12388,31 +12388,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="G62" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="H62" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="I62" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K62" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12427,10 +12427,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,14 +12560,14 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12582,31 +12582,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="G63" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="H63" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I63" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J63" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K63" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12621,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -12754,14 +12754,14 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12771,36 +12771,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="G64" t="n">
-        <v>14.5</v>
+        <v>2.06</v>
       </c>
       <c r="H64" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="K64" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.33</v>
+        <v>2.22</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,14 +12948,14 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12965,36 +12965,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LKP Motor Lublin</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="G65" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="H65" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="I65" t="n">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="J65" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13009,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -13142,14 +13142,14 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13159,66 +13159,66 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>LKP Motor Lublin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="G66" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="H66" t="n">
-        <v>5.8</v>
+        <v>1.86</v>
       </c>
       <c r="I66" t="n">
-        <v>6.2</v>
+        <v>2.16</v>
       </c>
       <c r="J66" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K66" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -13227,123 +13227,123 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AL66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM66" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN66" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO66" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AQ66" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AR66" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AS66" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT66" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BC66" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE66" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13353,36 +13353,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="G67" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="H67" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I67" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J67" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="K67" t="n">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -13397,10 +13397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13530,14 +13530,14 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13547,66 +13547,66 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="G68" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="H68" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="I68" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K68" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P68" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -13615,123 +13615,123 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO68" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG68" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13746,61 +13746,61 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="H69" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="I69" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="J69" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="K69" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="R69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -13809,123 +13809,123 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK69" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL69" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM69" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN69" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AO69" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS69" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AT69" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AU69" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV69" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW69" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AX69" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB69" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BC69" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BE69" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BG69" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13940,31 +13940,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G70" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="H70" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I70" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K70" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -14112,14 +14112,14 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14134,61 +14134,61 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="G71" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="H71" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>1.81</v>
       </c>
       <c r="J71" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="K71" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P71" t="n">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -14197,123 +14197,123 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO71" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AP71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR71" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS71" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU71" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW71" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY71" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA71" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG71" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14323,36 +14323,36 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Nacional Potosi</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -14500,14 +14500,14 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14517,191 +14517,191 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="G73" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="H73" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J73" t="n">
         <v>3.15</v>
       </c>
-      <c r="I73" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K73" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L73" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R73" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ73" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL73" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM73" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AO73" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AP73" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AQ73" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AR73" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS73" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AT73" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AV73" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AW73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX73" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AY73" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AZ73" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BA73" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BC73" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BD73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BE73" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14711,36 +14711,36 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -14888,14 +14888,14 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14905,191 +14905,191 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G75" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H75" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I75" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J75" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K75" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P75" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP75" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS75" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW75" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX75" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA75" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG75" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15099,33 +15099,33 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="G76" t="n">
-        <v>1.57</v>
+        <v>1000</v>
       </c>
       <c r="H76" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I76" t="n">
         <v>1000</v>
       </c>
       <c r="J76" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K76" t="n">
         <v>950</v>
@@ -15143,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -15276,14 +15276,14 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15293,36 +15293,36 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,14 +15470,14 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15487,33 +15487,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G78" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="H78" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I78" t="n">
         <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K78" t="n">
         <v>950</v>
@@ -15531,140 +15531,528 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:36:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q79" t="n">
         <v>1.01</v>
       </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH78" t="inlineStr">
-        <is>
-          <t>2026-04-30 03:17:28</t>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:36:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K80" t="n">
+        <v>950</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
